--- a/develop/ValueSet-mii-vs-fall-diagnosis-use.xlsx
+++ b/develop/ValueSet-mii-vs-fall-diagnosis-use.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="33">
   <si>
     <t>Property</t>
   </si>
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-10</t>
+    <t>2026-06-15</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -90,6 +90,9 @@
   </si>
   <si>
     <t>Purpose</t>
+  </si>
+  <si>
+    <t>Define allowed diagnosis usage roles in relation to an encounter.</t>
   </si>
   <si>
     <t>Copyright</t>
@@ -351,20 +354,22 @@
       <c r="A13" t="s" s="2">
         <v>24</v>
       </c>
-      <c r="B13" s="2"/>
+      <c r="B13" t="s" s="2">
+        <v>25</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -383,12 +388,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -407,12 +412,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -431,12 +436,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
